--- a/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/04_BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_v2.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-05_Accounting_Disbursement_ACSL/04_BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_v2.1.xlsx
@@ -59421,8 +59421,7 @@
       <c r="L544" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-093: "Enter a name"
-MSG-AC-094: "The saved parameter variant is deleted."</t>
+MSG-AC-093: "Enter the name of the variant."</t>
         </is>
       </c>
       <c r="M544" s="12" t="inlineStr">
@@ -59497,12 +59496,12 @@
       <c r="L545" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-098: "Choose at least one figure"
-MSG-AC-100: "Enter the as-of date"
-MSG-AC-103: "Only a balance schedule can be aged"
-MSG-AC-105: "Select a schedule"
-MSG-AC-106: "Starts after the as-of date"
-MSG-AC-107: "Use 2 to 40 letters, digits or dashes"</t>
+MSG-AC-097: "Choose at least one figure"
+MSG-AC-099: "Enter the as-of date"
+MSG-AC-102: "Only a balance schedule can be aged"
+MSG-AC-104: "Select a schedule"
+MSG-AC-105: "Starts after the as-of date"
+MSG-AC-106: "Use 2 to 40 letters, digits or dashes"</t>
         </is>
       </c>
       <c r="M545" s="12" t="inlineStr">
@@ -59577,10 +59576,10 @@
       <c r="L546" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-110: "Run &lt;run no&gt; has no invoice to pay a fee on" (SERVICE_FEE_EMPTY)
-MSG-AC-111: "The run is approved by someone other than its preparer" (SERVICE_FEE_FOUR_EYES)
-MSG-AC-112: "No invoice fully paid from &lt;from&gt; to &lt;to&gt; is left for a service fee / (&lt;size&gt; paid invoice(s) have no rule)" (SERVICE_FEE_NOTHING)
-MSG-AC-113: "Give a period that ends on or before today and after it starts" (SERVICE_FEE_PERIOD)</t>
+MSG-AC-109: "Run &lt;run no&gt; has no invoice to pay a fee on" (SERVICE_FEE_EMPTY)
+MSG-AC-110: "The run is approved by someone other than its preparer" (SERVICE_FEE_FOUR_EYES)
+MSG-AC-111: "No invoice fully paid from &lt;from&gt; to &lt;to&gt; is left for a service fee / (&lt;size&gt; paid invoice(s) have no rule)" (SERVICE_FEE_NOTHING)
+MSG-AC-112: "Give a period that ends on or before today and after it starts" (SERVICE_FEE_PERIOD)</t>
         </is>
       </c>
       <c r="M546" s="12" t="inlineStr">
@@ -59655,20 +59654,20 @@
       <c r="L547" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-115: "Ends before it starts"
-MSG-AC-116: "Enter a rate above 0 and up to 100"
-MSG-AC-117: "Enter the &lt;label&gt;"
-MSG-AC-118: "Enter the first day of the period"
-MSG-AC-119: "Enter the last day of the period"
-MSG-AC-120: "List the market segments covered"
-MSG-AC-122: "Select the service-fee segment"
-MSG-AC-123: "The period cannot end after today"
-MSG-AC-124: "The period ends before it starts"
-MSG-AC-125: "Give a date that is not in the future" (SERVICE_FEE_DATES)
-MSG-AC-126: "The liquidation date is before the release date &lt;released on&gt;" (SERVICE_FEE_DATES)
-MSG-AC-127: "Line &lt;line no&gt; is &lt;status&gt; and cannot be &lt;action&gt;" (SERVICE_FEE_LINE_STATUS)
-MSG-AC-128: "Attach the liquidation report of the unit" (SERVICE_FEE_LIQUIDATION_REPORT)
-MSG-AC-129: "Run &lt;run no&gt; is &lt;stage&gt; and cannot be &lt;action&gt;" (SERVICE_FEE_STAGE)</t>
+MSG-AC-114: "Ends before it starts"
+MSG-AC-115: "Enter a rate above 0 and up to 100"
+MSG-AC-116: "Enter the &lt;label&gt;"
+MSG-AC-117: "Enter the first day of the period"
+MSG-AC-118: "Enter the last day of the period"
+MSG-AC-119: "List the market segments covered"
+MSG-AC-121: "Select the service-fee segment"
+MSG-AC-122: "The period cannot end after today"
+MSG-AC-123: "The period ends before it starts"
+MSG-AC-124: "Give a date that is not in the future" (SERVICE_FEE_DATES)
+MSG-AC-125: "The liquidation date is before the release date &lt;released on&gt;" (SERVICE_FEE_DATES)
+MSG-AC-126: "Line &lt;line no&gt; is &lt;status&gt; and cannot be &lt;action&gt;" (SERVICE_FEE_LINE_STATUS)
+MSG-AC-127: "Attach the liquidation report of the unit" (SERVICE_FEE_LIQUIDATION_REPORT)
+MSG-AC-128: "Run &lt;run no&gt; is &lt;stage&gt; and cannot be &lt;action&gt;" (SERVICE_FEE_STAGE)</t>
         </is>
       </c>
       <c r="M547" s="12" t="inlineStr">
@@ -59743,13 +59742,13 @@
       <c r="L548" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-132: "Service-fee recipient already exists: &lt;key&gt;" (DUPLICATE)
-MSG-AC-133: "The rule ends before it starts" (SERVICE_FEE_DATES)
-MSG-AC-134: "The rate is a percentage above 0" (SERVICE_FEE_RATE)
-MSG-AC-135: "Give the payee code and name of the recipient" (SERVICE_FEE_RECIPIENT)
-MSG-AC-136: "Give the segment, the rate and the start date" (SERVICE_FEE_RULE)
-MSG-AC-137: "List the market segments the rule covers" (SERVICE_FEE_RULE)
-MSG-AC-138: "Give the sales unit" (SERVICE_FEE_UNIT)</t>
+MSG-AC-131: "Service-fee recipient already exists: &lt;key&gt;" (DUPLICATE)
+MSG-AC-132: "The rule ends before it starts" (SERVICE_FEE_DATES)
+MSG-AC-133: "The rate is a percentage above 0" (SERVICE_FEE_RATE)
+MSG-AC-134: "Give the payee code and name of the recipient" (SERVICE_FEE_RECIPIENT)
+MSG-AC-135: "Give the segment, the rate and the start date" (SERVICE_FEE_RULE)
+MSG-AC-136: "List the market segments the rule covers" (SERVICE_FEE_RULE)
+MSG-AC-137: "Give the sales unit" (SERVICE_FEE_UNIT)</t>
         </is>
       </c>
       <c r="M548" s="12" t="inlineStr">
@@ -59825,14 +59824,14 @@
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
 MSG-AC-140: "&lt;ok&gt; approved; &lt;length&gt; failed: &lt;failed[0]&gt;"
-MSG-AC-142: "The documents are released to the payee."
-MSG-AC-144: "A payment request needs a positive amount" (DISB_AMOUNT)
-MSG-AC-145: "Only BIR 2307 requests are released without a voucher" (DISB_NOT_A_RELEASE)
-MSG-AC-146: "Maintain payee &lt;payee code&gt; before creating the voucher" (DISB_PAYEE_NOT_MAINTAINED)
-MSG-AC-147: "Request &lt;source ref&gt; was already received" (DISB_REQUEST_DUPLICATE)
-MSG-AC-148: "Cancel or reject the voucher of &lt;request no&gt;" (DISB_REQUEST_IN_VOUCHER)
-MSG-AC-149: "Request &lt;request no&gt; is &lt;status&gt;" (DISB_REQUEST_STATUS)
-MSG-AC-150: "Request &lt;request no&gt; is &lt;status&gt; and cannot be &lt;action&gt;" (DISB_REQUEST_STATUS)</t>
+MSG-AC-141: "The documents are released to the payee."
+MSG-AC-143: "A payment request needs a positive amount" (DISB_AMOUNT)
+MSG-AC-144: "Only BIR 2307 requests are released without a voucher" (DISB_NOT_A_RELEASE)
+MSG-AC-145: "Maintain payee &lt;payee code&gt; before creating the voucher" (DISB_PAYEE_NOT_MAINTAINED)
+MSG-AC-146: "Request &lt;source ref&gt; was already received" (DISB_REQUEST_DUPLICATE)
+MSG-AC-147: "Cancel or reject the voucher of &lt;request no&gt;" (DISB_REQUEST_IN_VOUCHER)
+MSG-AC-148: "Request &lt;request no&gt; is &lt;status&gt;" (DISB_REQUEST_STATUS)
+MSG-AC-149: "Request &lt;request no&gt; is &lt;status&gt; and cannot be &lt;action&gt;" (DISB_REQUEST_STATUS)</t>
         </is>
       </c>
       <c r="M549" s="12" t="inlineStr">
@@ -59907,29 +59906,29 @@
       <c r="L550" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-153: "Enter an amount above zero"
-MSG-AC-154: "Enter the &lt;field label&gt;"
-MSG-AC-155: "Enter the expense account of an other disbursement"
-MSG-AC-156: "Enter the purpose"
-MSG-AC-157: "Enter the value date"
-MSG-AC-158: "Select a target account other than the source"
-MSG-AC-159: "Select the payee account credited"
-MSG-AC-160: "Select the paying account"
-MSG-AC-161: "Select the source account"
-MSG-AC-163: "The withholding tax must be at least zero and below the gross"
-MSG-AC-164: "The allocation must add up to the gross amount &lt;to plain string&gt;" (DV_ALLOCATION_TOTAL)
-MSG-AC-165: "The paying account must be in &lt;currency&gt;" (DV_BANK_CURRENCY)
-MSG-AC-166: "DV &lt;dv no&gt; has no entry" (DV_ENTRY_EMPTY)
-MSG-AC-167: "The withholding tax must be at least zero and below the gross amount" (DV_EWT)
-MSG-AC-168: "The approver of a voucher cannot be its processor or checker" (DV_FOUR_EYES)
-MSG-AC-169: "The processor cannot check their own voucher" (DV_FOUR_EYES)
-MSG-AC-170: "Complete DV &lt;dv no&gt;: &lt;missing&gt;" (DV_INCOMPLETE)
-MSG-AC-171: "Mode &lt;mode&gt; is not allowed for payee &lt;payee code&gt;" (DV_MODE)
-MSG-AC-172: "DV &lt;dv no&gt; is &lt;stage&gt; and can no longer be changed" (DV_NOT_EDITABLE)
-MSG-AC-173: "DV &lt;dv no&gt; is &lt;stage&gt;; return it first" (DV_NOT_EDITABLE)
-MSG-AC-174: "DV &lt;dv no&gt; is &lt;stage&gt;" (DV_NOT_FOR_APPROVAL)
-MSG-AC-175: "Select an active account of the payee" (DV_PAYEE_ACCOUNT)
-MSG-AC-176: "DV &lt;dv no&gt; could not be posted: &lt;message&gt;" (DV_POSTING_FAILED)</t>
+MSG-AC-152: "Enter an amount above zero"
+MSG-AC-153: "Enter the &lt;field label&gt;"
+MSG-AC-154: "Enter the expense account of an other disbursement"
+MSG-AC-155: "Enter the purpose"
+MSG-AC-156: "Enter the value date"
+MSG-AC-157: "Select a target account other than the source"
+MSG-AC-158: "Select the payee account credited"
+MSG-AC-159: "Select the paying account"
+MSG-AC-160: "Select the source account"
+MSG-AC-162: "The withholding tax must be at least zero and below the gross"
+MSG-AC-163: "The allocation must add up to the gross amount &lt;to plain string&gt;" (DV_ALLOCATION_TOTAL)
+MSG-AC-164: "The paying account must be in &lt;currency&gt;" (DV_BANK_CURRENCY)
+MSG-AC-165: "DV &lt;dv no&gt; has no entry" (DV_ENTRY_EMPTY)
+MSG-AC-166: "The withholding tax must be at least zero and below the gross amount" (DV_EWT)
+MSG-AC-167: "The approver of a voucher cannot be its processor or checker" (DV_FOUR_EYES)
+MSG-AC-168: "The processor cannot check their own voucher" (DV_FOUR_EYES)
+MSG-AC-169: "Complete DV &lt;dv no&gt;: &lt;missing&gt;" (DV_INCOMPLETE)
+MSG-AC-170: "Mode &lt;mode&gt; is not allowed for payee &lt;payee code&gt;" (DV_MODE)
+MSG-AC-171: "DV &lt;dv no&gt; is &lt;stage&gt; and can no longer be changed" (DV_NOT_EDITABLE)
+MSG-AC-172: "DV &lt;dv no&gt; is &lt;stage&gt;; return it first" (DV_NOT_EDITABLE)
+MSG-AC-173: "DV &lt;dv no&gt; is &lt;stage&gt;" (DV_NOT_FOR_APPROVAL)
+MSG-AC-174: "Select an active account of the payee" (DV_PAYEE_ACCOUNT)
+MSG-AC-175: "DV &lt;dv no&gt; could not be posted: &lt;message&gt;" (DV_POSTING_FAILED)</t>
         </is>
       </c>
       <c r="M550" s="12" t="inlineStr">
@@ -60004,8 +60003,8 @@
       <c r="L551" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-180: "The proforma entry has no line" (DV_ENTRY_EMPTY)
-MSG-AC-181: "Select the paying bank account" (DV_INCOMPLETE)</t>
+MSG-AC-179: "The proforma entry has no line" (DV_ENTRY_EMPTY)
+MSG-AC-180: "Select the paying bank account" (DV_INCOMPLETE)</t>
         </is>
       </c>
       <c r="M551" s="12" t="inlineStr">
@@ -60080,18 +60079,18 @@
       <c r="L552" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-187: "The instrument status is changed as requested."
-MSG-AC-188: "Only a stale check is re-issued" (CHECK_NOT_STALE)
-MSG-AC-189: "Only an authority to debit is e-mailed" (DISB_NOT_ATD)
-MSG-AC-190: "&lt;mode&gt; has no printed form; it is processed by file" (DISB_NO_FORM)
-MSG-AC-191: "Mode &lt;mode&gt; has no printed form" (DISB_NO_FORM)
-MSG-AC-192: "The DV has no instrument until it is approved" (DV_NOT_APPROVED)
-MSG-AC-193: "&lt;mode&gt; &lt;label&gt; is &lt;status&gt; and cannot be cancelled" (INSTRUMENT_FINAL)
-MSG-AC-194: "&lt;mode&gt; &lt;label&gt; is &lt;status&gt; and cannot become &lt;to&gt;" (INSTRUMENT_STATUS)
-MSG-AC-195: "A status edit cannot be approved by its requestor" (MAKER_CHECKER_VIOLATION)
-MSG-AC-196: "&lt;to&gt; is not another status of a &lt;mode&gt;" (STATUS_EDIT_INVALID)
-MSG-AC-197: "A status edit of this instrument already waits for approval" (STATUS_EDIT_PENDING)
-MSG-AC-198: "The instrument is now &lt;status&gt;; request the edit again" (STATUS_EDIT_STALE)</t>
+MSG-AC-186: "The instrument status is changed as requested."
+MSG-AC-187: "Only a stale check is re-issued" (CHECK_NOT_STALE)
+MSG-AC-188: "Only an authority to debit is e-mailed" (DISB_NOT_ATD)
+MSG-AC-189: "&lt;mode&gt; has no printed form; it is processed by file" (DISB_NO_FORM)
+MSG-AC-190: "Mode &lt;mode&gt; has no printed form" (DISB_NO_FORM)
+MSG-AC-191: "The DV has no instrument until it is approved" (DV_NOT_APPROVED)
+MSG-AC-192: "&lt;mode&gt; &lt;label&gt; is &lt;status&gt; and cannot be cancelled" (INSTRUMENT_FINAL)
+MSG-AC-193: "&lt;mode&gt; &lt;label&gt; is &lt;status&gt; and cannot become &lt;to&gt;" (INSTRUMENT_STATUS)
+MSG-AC-194: "A status edit cannot be approved by its requestor" (MAKER_CHECKER_VIOLATION)
+MSG-AC-195: "&lt;to&gt; is not another status of a &lt;mode&gt;" (STATUS_EDIT_INVALID)
+MSG-AC-196: "A status edit of this instrument already waits for approval" (STATUS_EDIT_PENDING)
+MSG-AC-197: "The instrument is now &lt;status&gt;; request the edit again" (STATUS_EDIT_STALE)</t>
         </is>
       </c>
       <c r="M552" s="12" t="inlineStr">
@@ -60166,8 +60165,8 @@
       <c r="L553" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-201: "The period covered ends before it starts" (CWT_PERIOD)
-MSG-AC-202: "Only an approved DV is tagged; DV &lt;dv no&gt; is &lt;stage&gt;" (DV_NOT_APPROVED)</t>
+MSG-AC-200: "The period covered ends before it starts" (CWT_PERIOD)
+MSG-AC-201: "Only an approved DV is tagged; DV &lt;dv no&gt; is &lt;stage&gt;" (DV_NOT_APPROVED)</t>
         </is>
       </c>
       <c r="M553" s="12" t="inlineStr">
@@ -60242,7 +60241,7 @@
       <c r="L554" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-205: "The payee request is &lt;status&gt;" (PAYEE_REQUEST_CLOSED)</t>
+MSG-AC-204: "The payee request is &lt;status&gt;" (PAYEE_REQUEST_CLOSED)</t>
         </is>
       </c>
       <c r="M554" s="12" t="inlineStr">
@@ -60317,24 +60316,24 @@
       <c r="L555" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-207: "A credit mode needs a bank account of the payee"
-MSG-AC-210: "Enter a 3-letter currency"
-MSG-AC-211: "Enter a valid e-mail"
-MSG-AC-212: "Enter the account name"
-MSG-AC-213: "Enter the account number (digits)"
-MSG-AC-214: "Enter the bank"
-MSG-AC-215: "Enter the payee (party) code"
-MSG-AC-216: "Enter the payee name"
-MSG-AC-221: "Select the payee class"
-MSG-AC-222: "The payee is deleted; it was never used on a payment."
-MSG-AC-223: "Disbursement payee already exists: &lt;key&gt;" (DUPLICATE)
-MSG-AC-224: "A payee cannot be authorised by the user who maintained it" (MAKER_CHECKER_VIOLATION)
-MSG-AC-225: "Company and payee code are required" (PAYEE_CODE)
-MSG-AC-226: "Only a draft payee never used can be deleted; deactivate it instead" (PAYEE_IN_USE)
-MSG-AC-227: "Select at least one mode of payment" (PAYEE_MODE)
-MSG-AC-228: "The default mode of payment must be one of the allowed modes" (PAYEE_MODE)
-MSG-AC-229: "Payee &lt;payee code&gt; is &lt;stage&gt;" (PAYEE_NOT_EDITABLE)
-MSG-AC-230: "Payee &lt;payee code&gt; was not migrated" (PAYEE_NOT_MIGRATED)</t>
+MSG-AC-206: "A credit mode needs a bank account of the payee"
+MSG-AC-209: "Enter a 3-letter currency"
+MSG-AC-210: "Enter a valid e-mail"
+MSG-AC-211: "Enter the account name"
+MSG-AC-212: "Enter the account number (digits)"
+MSG-AC-213: "Enter the bank"
+MSG-AC-214: "Enter the payee (party) code"
+MSG-AC-215: "Enter the payee name"
+MSG-AC-220: "Select the payee class"
+MSG-AC-221: "The payee is deleted; it was never used on a payment."
+MSG-AC-222: "Disbursement payee already exists: &lt;key&gt;" (DUPLICATE)
+MSG-AC-223: "A payee cannot be authorised by the user who maintained it" (MAKER_CHECKER_VIOLATION)
+MSG-AC-224: "Company and payee code are required" (PAYEE_CODE)
+MSG-AC-225: "Only a draft payee never used can be deleted; deactivate it instead" (PAYEE_IN_USE)
+MSG-AC-226: "Select at least one mode of payment" (PAYEE_MODE)
+MSG-AC-227: "The default mode of payment must be one of the allowed modes" (PAYEE_MODE)
+MSG-AC-228: "Payee &lt;payee code&gt; is &lt;stage&gt;" (PAYEE_NOT_EDITABLE)
+MSG-AC-229: "Payee &lt;payee code&gt; was not migrated" (PAYEE_NOT_MIGRATED)</t>
         </is>
       </c>
       <c r="M555" s="12" t="inlineStr">
@@ -60409,10 +60408,10 @@
       <c r="L556" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-231: "No printed or released check &lt;check no&gt; (&lt;size&gt; found)" (CHECK_NOT_FOUND)
-MSG-AC-232: "No DV &lt;dv no&gt;" (DV_NOT_FOUND)
-MSG-AC-233: "Amount &lt;amount&gt; differs from &lt;to plain string&gt; of &lt;label&gt;" (INSTRUMENT_AMOUNT)
-MSG-AC-234: "DV &lt;dv no&gt; is paid by &lt;mode&gt;, not &lt;mode&gt;" (INSTRUMENT_MODE)</t>
+MSG-AC-230: "No printed or released check &lt;check no&gt; (&lt;size&gt; found)" (CHECK_NOT_FOUND)
+MSG-AC-231: "No DV &lt;dv no&gt;" (DV_NOT_FOUND)
+MSG-AC-232: "Amount &lt;amount&gt; differs from &lt;to plain string&gt; of &lt;label&gt;" (INSTRUMENT_AMOUNT)
+MSG-AC-233: "DV &lt;dv no&gt; is paid by &lt;mode&gt;, not &lt;mode&gt;" (INSTRUMENT_MODE)</t>
         </is>
       </c>
       <c r="M556" s="12" t="inlineStr">
@@ -60487,8 +60486,8 @@
       <c r="L557" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-238: "The end of day of &lt;business date&gt; was already processed" (EOD_ALREADY_RUN)
-MSG-AC-239: "The confirmations of &lt;run no&gt; were already sent" (EOD_CONFIRMED)</t>
+MSG-AC-237: "The end of day of &lt;business date&gt; was already processed" (EOD_ALREADY_RUN)
+MSG-AC-238: "The confirmations of &lt;run no&gt; were already sent" (EOD_CONFIRMED)</t>
         </is>
       </c>
       <c r="M557" s="12" t="inlineStr">
@@ -60563,14 +60562,14 @@
       <c r="L558" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-241: "The amount must be positive" (FUNDING_AMOUNT)
-MSG-AC-242: "Select the company" (FUNDING_COMPANY)
-MSG-AC-243: "Both accounts must be in &lt;currency&gt;" (FUNDING_CURRENCY)
-MSG-AC-244: "The maker cannot verify the funding request" (FUNDING_FOUR_EYES)
-MSG-AC-245: "The maker or verifier cannot approve the funding request" (FUNDING_FOUR_EYES)
-MSG-AC-246: "The second approval must be given by another approver" (FUNDING_FOUR_EYES)
-MSG-AC-247: "Funding request &lt;funding no&gt; is &lt;stage&gt;" (FUNDING_NOT_EDITABLE)
-MSG-AC-248: "The source and target accounts must differ" (FUNDING_SAME_ACCOUNT)</t>
+MSG-AC-240: "The amount must be positive" (FUNDING_AMOUNT)
+MSG-AC-241: "Select the company" (FUNDING_COMPANY)
+MSG-AC-242: "Both accounts must be in &lt;currency&gt;" (FUNDING_CURRENCY)
+MSG-AC-243: "The maker cannot verify the funding request" (FUNDING_FOUR_EYES)
+MSG-AC-244: "The maker or verifier cannot approve the funding request" (FUNDING_FOUR_EYES)
+MSG-AC-245: "The second approval must be given by another approver" (FUNDING_FOUR_EYES)
+MSG-AC-246: "Funding request &lt;funding no&gt; is &lt;stage&gt;" (FUNDING_NOT_EDITABLE)
+MSG-AC-247: "The source and target accounts must differ" (FUNDING_SAME_ACCOUNT)</t>
         </is>
       </c>
       <c r="M558" s="12" t="inlineStr">
@@ -60645,36 +60644,36 @@
       <c r="L559" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-263: "Add at least one account"
-MSG-AC-264: "All accounts of a refund request belong to one client"
-MSG-AC-265: "Check Cancellation"
-MSG-AC-266: "Enter a positive amount with at most two decimals"
-MSG-AC-267: "Enter the account number (10 to 16 digits)"
-MSG-AC-268: "Enter the employee name"
-MSG-AC-269: "Enter the employee number"
-MSG-AC-270: "Enter the purpose"
-MSG-AC-272: "Select the mode of payment"
-MSG-AC-273: "The amount must be positive with at most two decimals" (PRQ_AMOUNT_INVALID)
-MSG-AC-274: "A cancellation of the check of &lt;request no&gt; is already in progress" (PRQ_CANCELLATION_PENDING)
-MSG-AC-275: "Currency must be a 3-letter code" (PRQ_CURRENCY_INVALID)
-MSG-AC-276: "AR &lt;ar no&gt; appears twice on the request" (PRQ_DUPLICATE_AR)
-MSG-AC-277: "AR &lt;first[0]&gt; is already refunded by request &lt;first[1]&gt;" (PRQ_DUPLICATE_AR)
-MSG-AC-278: "You raised or already moved &lt;request no&gt;: another user decides" (PRQ_FOUR_EYES)
-MSG-AC-279: "Invoice &lt;invoice no&gt; is not in the ledger" (PRQ_INVOICE_UNKNOWN)
-MSG-AC-280: "A refund request has between 1 and 50 accounts" (PRQ_LINES_REQUIRED)
-MSG-AC-281: "Every line needs the AR number and the assured name" (PRQ_LINE_INCOMPLETE)
-MSG-AC-282: "The company has no branch" (PRQ_NO_BRANCH)
-MSG-AC-283: "A check cancellation has no request form; print the paid request's" (PRQ_NO_FORM)
-MSG-AC-284: "&lt;request no&gt; has no liquidation yet" (PRQ_NO_LIQUIDATION)
-MSG-AC-285: "All accounts of a refund request belong to one client" (PRQ_ONE_CLIENT)
-MSG-AC-286: "Give the payee code and name" (PRQ_PAYEE_REQUIRED)
-MSG-AC-287: "Give the purpose of the cash advance" (PRQ_PURPOSE_REQUIRED)
-MSG-AC-288: "&lt;request no&gt; was not paid by check" (PRQ_TARGET_NOT_CHECK)
-MSG-AC-289: "&lt;request no&gt; has no disbursement voucher yet" (PRQ_TARGET_NOT_DISBURSED)
-MSG-AC-290: "Request &lt;target request no&gt; is not a refund or cash advance" (PRQ_TARGET_UNKNOWN)
-MSG-AC-291: "This validation was already &lt;status&gt;" (PRQ_VALIDATION_DONE)
-MSG-AC-292: "&lt;request no&gt; can no longer be changed (&lt;stage&gt;)" (PRQ_WRONG_STAGE)
-MSG-AC-293: "&lt;request no&gt; is &lt;stage&gt; for this action" (PRQ_WRONG_STAGE)</t>
+MSG-AC-262: "Add at least one account"
+MSG-AC-263: "All accounts of a refund request belong to one client"
+MSG-AC-264: "Check Cancellation"
+MSG-AC-265: "Enter a positive amount with at most two decimals"
+MSG-AC-266: "Enter the account number (10 to 16 digits)"
+MSG-AC-267: "Enter the employee name"
+MSG-AC-268: "Enter the employee number"
+MSG-AC-269: "Enter the purpose"
+MSG-AC-271: "Select the mode of payment"
+MSG-AC-272: "The amount must be positive with at most two decimals" (PRQ_AMOUNT_INVALID)
+MSG-AC-273: "A cancellation of the check of &lt;request no&gt; is already in progress" (PRQ_CANCELLATION_PENDING)
+MSG-AC-274: "Currency must be a 3-letter code" (PRQ_CURRENCY_INVALID)
+MSG-AC-275: "AR &lt;ar no&gt; appears twice on the request" (PRQ_DUPLICATE_AR)
+MSG-AC-276: "AR &lt;first[0]&gt; is already refunded by request &lt;first[1]&gt;" (PRQ_DUPLICATE_AR)
+MSG-AC-277: "You raised or already moved &lt;request no&gt;: another user decides" (PRQ_FOUR_EYES)
+MSG-AC-278: "Invoice &lt;invoice no&gt; is not in the ledger" (PRQ_INVOICE_UNKNOWN)
+MSG-AC-279: "A refund request has between 1 and 50 accounts" (PRQ_LINES_REQUIRED)
+MSG-AC-280: "Every line needs the AR number and the assured name" (PRQ_LINE_INCOMPLETE)
+MSG-AC-281: "The company has no branch" (PRQ_NO_BRANCH)
+MSG-AC-282: "A check cancellation has no request form; print the paid request's" (PRQ_NO_FORM)
+MSG-AC-283: "&lt;request no&gt; has no liquidation yet" (PRQ_NO_LIQUIDATION)
+MSG-AC-284: "All accounts of a refund request belong to one client" (PRQ_ONE_CLIENT)
+MSG-AC-285: "Give the payee code and name" (PRQ_PAYEE_REQUIRED)
+MSG-AC-286: "Give the purpose of the cash advance" (PRQ_PURPOSE_REQUIRED)
+MSG-AC-287: "&lt;request no&gt; was not paid by check" (PRQ_TARGET_NOT_CHECK)
+MSG-AC-288: "&lt;request no&gt; has no disbursement voucher yet" (PRQ_TARGET_NOT_DISBURSED)
+MSG-AC-289: "Request &lt;target request no&gt; is not a refund or cash advance" (PRQ_TARGET_UNKNOWN)
+MSG-AC-290: "This validation was already &lt;status&gt;" (PRQ_VALIDATION_DONE)
+MSG-AC-291: "&lt;request no&gt; can no longer be changed (&lt;stage&gt;)" (PRQ_WRONG_STAGE)
+MSG-AC-292: "&lt;request no&gt; is &lt;stage&gt; for this action" (PRQ_WRONG_STAGE)</t>
         </is>
       </c>
       <c r="M559" s="12" t="inlineStr">
@@ -60749,13 +60748,13 @@
       <c r="L560" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-294: "Expenses are zero or positive with at most two decimals" (PRQ_AMOUNT_INVALID)
-MSG-AC-295: "A liquidation is checked by someone other than the employee" (PRQ_FOUR_EYES)
-MSG-AC-296: "Enter at least one fieldwork day before submitting" (PRQ_LIQUIDATION_EMPTY)
-MSG-AC-297: "Every fieldwork day needs its date and particulars" (PRQ_LIQUIDATION_LINE)
-MSG-AC-298: "A liquidation has up to 60 fieldwork days" (PRQ_LIQUIDATION_LINES)
-MSG-AC-299: "&lt;liquidation no&gt; is &lt;status&gt;" (PRQ_LIQUIDATION_LOCKED)
-MSG-AC-300: "Only a disbursed cash advance is liquidated" (PRQ_NOT_LIQUIDABLE)</t>
+MSG-AC-293: "Expenses are zero or positive with at most two decimals" (PRQ_AMOUNT_INVALID)
+MSG-AC-294: "A liquidation is checked by someone other than the employee" (PRQ_FOUR_EYES)
+MSG-AC-295: "Enter at least one fieldwork day before submitting" (PRQ_LIQUIDATION_EMPTY)
+MSG-AC-296: "Every fieldwork day needs its date and particulars" (PRQ_LIQUIDATION_LINE)
+MSG-AC-297: "A liquidation has up to 60 fieldwork days" (PRQ_LIQUIDATION_LINES)
+MSG-AC-298: "&lt;liquidation no&gt; is &lt;status&gt;" (PRQ_LIQUIDATION_LOCKED)
+MSG-AC-299: "Only a disbursed cash advance is liquidated" (PRQ_NOT_LIQUIDABLE)</t>
         </is>
       </c>
       <c r="M560" s="12" t="inlineStr">
@@ -60830,8 +60829,8 @@
       <c r="L561" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-302: "Comptrollership has not set the account of &lt;missing&gt; for liquidations" (PRQ_LIQUIDATION_ACCOUNT_MISSING)
-MSG-AC-303: "Give one of the roles &lt;roles&gt; and an account code" (PRQ_LIQUIDATION_ROLE)</t>
+MSG-AC-301: "Comptrollership has not set the account of &lt;missing&gt; for liquidations" (PRQ_LIQUIDATION_ACCOUNT_MISSING)
+MSG-AC-302: "Give one of the roles &lt;roles&gt; and an account code" (PRQ_LIQUIDATION_ROLE)</t>
         </is>
       </c>
       <c r="M561" s="12" t="inlineStr">
@@ -60906,7 +60905,7 @@
       <c r="L562" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-306: "&lt;reference&gt; is &lt;actual&gt;, not &lt;expected&gt;" (ACSL_WRONG_STAGE)</t>
+MSG-AC-305: "&lt;reference&gt; is &lt;actual&gt;, not &lt;expected&gt;" (ACSL_WRONG_STAGE)</t>
         </is>
       </c>
       <c r="M562" s="12" t="inlineStr">
@@ -60981,15 +60980,15 @@
       <c r="L563" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-309: "Record Findings"
-MSG-AC-310: "Required"
-MSG-AC-311: "Give the case type and subject" (ACSL_CASE_INCOMPLETE)
-MSG-AC-312: "Invoice &lt;invoice no&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
-MSG-AC-313: "The case's invoice has no Account Officer, or the message is empty" (ACSL_NO_ACCOUNT_OFFICER)
-MSG-AC-314: "Give the result: confirmed, rejected or no action" (ACSL_OUTCOME_INVALID)
-MSG-AC-315: "A payment reversal needs the case's invoice and the receipt" (ACSL_REVERSAL_INCOMPLETE)
-MSG-AC-316: "&lt;case no&gt; is &lt;stage&gt;" (ACSL_WRONG_STAGE)
-MSG-AC-317: "&lt;case no&gt; is &lt;stage&gt;: no request can be made" (ACSL_WRONG_STAGE)</t>
+MSG-AC-308: "Record Findings"
+MSG-AC-309: "Required"
+MSG-AC-310: "Give the case type and subject" (ACSL_CASE_INCOMPLETE)
+MSG-AC-311: "Invoice &lt;invoice no&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
+MSG-AC-312: "The case's invoice has no Account Officer, or the message is empty" (ACSL_NO_ACCOUNT_OFFICER)
+MSG-AC-313: "Give the result: confirmed, rejected or no action" (ACSL_OUTCOME_INVALID)
+MSG-AC-314: "A payment reversal needs the case's invoice and the receipt" (ACSL_REVERSAL_INCOMPLETE)
+MSG-AC-315: "&lt;case no&gt; is &lt;stage&gt;" (ACSL_WRONG_STAGE)
+MSG-AC-316: "&lt;case no&gt; is &lt;stage&gt;: no request can be made" (ACSL_WRONG_STAGE)</t>
         </is>
       </c>
       <c r="M563" s="12" t="inlineStr">
@@ -61064,23 +61063,23 @@
       <c r="L564" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-324: "Account &lt;code&gt; is a heading" (ACSL_ACCOUNT_NOT_POSTABLE)
-MSG-AC-325: "Account &lt;code&gt; is not in the chart" (ACSL_ACCOUNT_UNKNOWN)
-MSG-AC-326: "A ledger component (&lt;components&gt;) needs the invoice it corrects" (ACSL_COMPONENT_INVALID)
-MSG-AC-327: "A correction needs at least two lines and equal debits (&lt;to plain string&gt;) and credits (&lt;to plain string&gt;)" (ACSL_CORRECTION_UNBALANCED)
-MSG-AC-328: "Describe the correction" (ACSL_DESCRIPTION_REQUIRED)
-MSG-AC-329: "A correction is reviewed by someone other than its preparer" (ACSL_FOUR_EYES)
-MSG-AC-330: "The approver of a correction is not its maker" (ACSL_FOUR_EYES)
-MSG-AC-331: "Invoice &lt;invoice&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
-MSG-AC-332: "Invoice &lt;no&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
-MSG-AC-333: "Journal &lt;batch no&gt; not found" (ACSL_JOURNAL_UNKNOWN)
-MSG-AC-334: "Every line needs a GL account" (ACSL_LINE_INVALID)
-MSG-AC-335: "Every line needs a side and a positive amount with two decimals" (ACSL_LINE_INVALID)
-MSG-AC-336: "Journal &lt;batch no&gt; has no line &lt;line no&gt;" (ACSL_LINE_UNKNOWN)
-MSG-AC-337: "The company has no branch" (ACSL_NO_BRANCH)
-MSG-AC-338: "Control account &lt;code&gt; needs the sub-ledger party" (ACSL_PARTY_REQUIRED)
-MSG-AC-339: "Party &lt;code&gt; of a correction line is not maintained" (ACSL_PARTY_UNKNOWN)
-MSG-AC-340: "A correction has at most 200 lines" (ACSL_TOO_MANY_LINES)</t>
+MSG-AC-323: "Account &lt;code&gt; is a heading" (ACSL_ACCOUNT_NOT_POSTABLE)
+MSG-AC-324: "Account &lt;code&gt; is not in the chart" (ACSL_ACCOUNT_UNKNOWN)
+MSG-AC-325: "A ledger component (&lt;components&gt;) needs the invoice it corrects" (ACSL_COMPONENT_INVALID)
+MSG-AC-326: "A correction needs at least two lines and equal debits (&lt;to plain string&gt;) and credits (&lt;to plain string&gt;)" (ACSL_CORRECTION_UNBALANCED)
+MSG-AC-327: "Describe the correction" (ACSL_DESCRIPTION_REQUIRED)
+MSG-AC-328: "A correction is reviewed by someone other than its preparer" (ACSL_FOUR_EYES)
+MSG-AC-329: "The approver of a correction is not its maker" (ACSL_FOUR_EYES)
+MSG-AC-330: "Invoice &lt;invoice&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
+MSG-AC-331: "Invoice &lt;no&gt; is not in the ledger" (ACSL_INVOICE_UNKNOWN)
+MSG-AC-332: "Journal &lt;batch no&gt; not found" (ACSL_JOURNAL_UNKNOWN)
+MSG-AC-333: "Every line needs a GL account" (ACSL_LINE_INVALID)
+MSG-AC-334: "Every line needs a side and a positive amount with two decimals" (ACSL_LINE_INVALID)
+MSG-AC-335: "Journal &lt;batch no&gt; has no line &lt;line no&gt;" (ACSL_LINE_UNKNOWN)
+MSG-AC-336: "The company has no branch" (ACSL_NO_BRANCH)
+MSG-AC-337: "Control account &lt;code&gt; needs the sub-ledger party" (ACSL_PARTY_REQUIRED)
+MSG-AC-338: "Party &lt;code&gt; of a correction line is not maintained" (ACSL_PARTY_UNKNOWN)
+MSG-AC-339: "A correction has at most 200 lines" (ACSL_TOO_MANY_LINES)</t>
         </is>
       </c>
       <c r="M564" s="12" t="inlineStr">
@@ -61155,11 +61154,11 @@
       <c r="L565" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-343: "The file does not follow the layout '&lt;name&gt;'; missing column(s): &lt;missing&gt;" (ACSL_SOA_LAYOUT_MISMATCH)
-MSG-AC-344: "No SOA layout is configured" (ACSL_SOA_NO_LAYOUT)
-MSG-AC-345: "Give the insurer and the covered period of the statement" (ACSL_SOA_PERIOD)
-MSG-AC-346: "The covered period ends before it starts" (ACSL_SOA_PERIOD)
-MSG-AC-347: "An SOA upload has at most &lt;max&gt; rows" (ACSL_SOA_TOO_LARGE)</t>
+MSG-AC-342: "The file does not follow the layout '&lt;name&gt;'; missing column(s): &lt;missing&gt;" (ACSL_SOA_LAYOUT_MISMATCH)
+MSG-AC-343: "No SOA layout is configured" (ACSL_SOA_NO_LAYOUT)
+MSG-AC-344: "Give the insurer and the covered period of the statement" (ACSL_SOA_PERIOD)
+MSG-AC-345: "The covered period ends before it starts" (ACSL_SOA_PERIOD)
+MSG-AC-346: "An SOA upload has at most &lt;max&gt; rows" (ACSL_SOA_TOO_LARGE)</t>
         </is>
       </c>
       <c r="M565" s="12" t="inlineStr">
@@ -61234,7 +61233,7 @@
       <c r="L566" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-350: "The file must be at most 10 MB" (ACSL_SOA_TOO_LARGE)</t>
+MSG-AC-349: "The file must be at most 10 MB" (ACSL_SOA_TOO_LARGE)</t>
         </is>
       </c>
       <c r="M566" s="12" t="inlineStr">
@@ -61309,7 +61308,7 @@
       <c r="L567" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-354: "Give the sub-ledger, and the components (Operations ledger) or document types (open items)" (ACSL_GLSL_SETTING)</t>
+MSG-AC-353: "Give the sub-ledger, and the components (Operations ledger) or document types (open items)" (ACSL_GLSL_SETTING)</t>
         </is>
       </c>
       <c r="M567" s="12" t="inlineStr">
@@ -61372,6 +61371,7 @@
       <c r="L568" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
+MSG-AC-354: "Complete the required parameters first"
 MSG-AC-355: "The account becomes active and can be posted to."
 MSG-AC-356: "The bank account change takes effect."
 MSG-AC-357: "The request is closed without creating a payee."
@@ -61450,8 +61450,8 @@
       <c r="L569" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-359: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
-MSG-AC-360: "&lt;Column&gt; is mandatory"</t>
+MSG-AC-360: "&lt;Column&gt; '&lt;value&gt;' is not a valid &lt;number, date (yyyy-mm-dd), Y/N value&gt;"
+MSG-AC-361: "&lt;Column&gt; is mandatory"</t>
         </is>
       </c>
       <c r="M569" s="12" t="inlineStr">
@@ -61526,12 +61526,12 @@
       <c r="L570" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-361: "&lt;header&gt; must be one of &lt;details&gt;"
-MSG-AC-362: "Account &lt;code&gt; already exists"
-MSG-AC-363: "Account Code may hold digits, capital letters, '.' and '-' only"
-MSG-AC-364: "Currencies must be three-letter codes separated by commas"
-MSG-AC-365: "Enter the account code of a top-level account"
-MSG-AC-366: "Parent &lt;parent&gt; is neither an account nor an earlier row of the file"</t>
+MSG-AC-362: "&lt;header&gt; must be one of &lt;details&gt;"
+MSG-AC-363: "Account &lt;code&gt; already exists"
+MSG-AC-364: "Account Code may hold digits, capital letters, '.' and '-' only"
+MSG-AC-365: "Currencies must be three-letter codes separated by commas"
+MSG-AC-366: "Enter the account code of a top-level account"
+MSG-AC-367: "Parent &lt;parent&gt; is neither an account nor an earlier row of the file"</t>
         </is>
       </c>
       <c r="M570" s="12" t="inlineStr">
@@ -61606,9 +61606,9 @@
       <c r="L571" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-367: "The amount must be positive"
-MSG-AC-368: "The currency must be a 3-letter code"
-MSG-AC-370: "Unknown disbursement type &lt;type&gt;"</t>
+MSG-AC-368: "The amount must be positive"
+MSG-AC-369: "The currency must be a 3-letter code"
+MSG-AC-371: "Unknown disbursement type &lt;type&gt;"</t>
         </is>
       </c>
       <c r="M571" s="12" t="inlineStr">
@@ -61683,8 +61683,8 @@
       <c r="L572" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-369: "The default mode must be one of the allowed modes"
-MSG-AC-371: "Unknown mode of payment: &lt;message&gt;"</t>
+MSG-AC-370: "The default mode must be one of the allowed modes"
+MSG-AC-372: "Unknown mode of payment: &lt;message&gt;"</t>
         </is>
       </c>
       <c r="M572" s="12" t="inlineStr">
@@ -61747,13 +61747,13 @@
       <c r="L573" s="12" t="inlineStr">
         <is>
           <t>Each message is shown word for word, with its code as the Reference for a server message, and nothing is saved:
-MSG-AC-372: "You are not permitted to perform this action" (ACCESS_DENIED)
-MSG-AC-373: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
-MSG-AC-374: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
-MSG-AC-375: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
-MSG-AC-376: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
-MSG-AC-377: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
-MSG-AC-378: "Invalid request" (VALIDATION_FAILED)</t>
+MSG-AC-373: "You are not permitted to perform this action" (ACCESS_DENIED)
+MSG-AC-374: "The record was changed by another user. Please reload and try again." (CONCURRENT_MODIFICATION)
+MSG-AC-375: "The system could not complete the request. Try again; if it continues, contact support with the reference." (INTERNAL_ERROR)
+MSG-AC-376: "Parameter '&lt;name&gt;' has an invalid value" (MALFORMED_REQUEST)
+MSG-AC-377: "Required parameter '&lt;parameter name&gt;' is missing" (MALFORMED_REQUEST)
+MSG-AC-378: "The uploaded file is too large" (UPLOAD_TOO_LARGE)
+MSG-AC-379: "Invalid request" (VALIDATION_FAILED)</t>
         </is>
       </c>
       <c r="M573" s="12" t="inlineStr">
